--- a/artfynd/A 7718-2025 artfynd.xlsx
+++ b/artfynd/A 7718-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135947573</v>
       </c>
       <c r="B2" t="n">
-        <v>58703</v>
+        <v>58705</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 7718-2025 artfynd.xlsx
+++ b/artfynd/A 7718-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135947573</v>
       </c>
       <c r="B2" t="n">
-        <v>58705</v>
+        <v>58706</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 7718-2025 artfynd.xlsx
+++ b/artfynd/A 7718-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135947573</v>
       </c>
       <c r="B2" t="n">
-        <v>58706</v>
+        <v>58710</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 7718-2025 artfynd.xlsx
+++ b/artfynd/A 7718-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135947573</v>
       </c>
       <c r="B2" t="n">
-        <v>58710</v>
+        <v>58711</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 7718-2025 artfynd.xlsx
+++ b/artfynd/A 7718-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135947573</v>
       </c>
       <c r="B2" t="n">
-        <v>58711</v>
+        <v>58716</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 7718-2025 artfynd.xlsx
+++ b/artfynd/A 7718-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135947573</v>
       </c>
       <c r="B2" t="n">
-        <v>58716</v>
+        <v>58729</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
